--- a/OUTPUT/direct_Q88PE9_Pseudomonas_putida_KT2440.xlsx
+++ b/OUTPUT/direct_Q88PE9_Pseudomonas_putida_KT2440.xlsx
@@ -486,7 +486,7 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0.0018</v>
+        <v>0.001999200319872051</v>
       </c>
     </row>
     <row r="3">
@@ -515,7 +515,7 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0.022</v>
+        <v>0.02219112355057977</v>
       </c>
     </row>
     <row r="4">
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0.1832</v>
+        <v>0.1833266693322671</v>
       </c>
     </row>
     <row r="5">
@@ -573,7 +573,7 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0.9202</v>
+        <v>0.9200319872051179</v>
       </c>
     </row>
     <row r="6">
@@ -602,7 +602,7 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0.9202</v>
+        <v>0.9200319872051179</v>
       </c>
     </row>
   </sheetData>
